--- a/tools/importer/reports/import-road-trip.report.xlsx
+++ b/tools/importer/reports/import-road-trip.report.xlsx
@@ -52,7 +52,7 @@
     <t>road-trip</t>
   </si>
   <si>
-    <t>2026-08-27T05:44:14.306Z</t>
+    <t>2026-08-29T10:41:06.737Z</t>
   </si>
   <si>
     <t>Road trip through Central Australia | RACQ</t>

--- a/tools/importer/reports/import-road-trip.report.xlsx
+++ b/tools/importer/reports/import-road-trip.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,19 +37,34 @@
     <t>url</t>
   </si>
   <si>
+    <t>articles/road-trip/10-of-the-most-interesting-car-models-headed-our-way.report.json</t>
+  </si>
+  <si>
+    <t>["hero-newsletter","cards-article-list","cards-related"]</t>
+  </si>
+  <si>
+    <t>articles/road-trip/10-of-the-most-interesting-car-models-headed-our-way</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>road-trip</t>
+  </si>
+  <si>
+    <t>2026-09-01T13:41:54.980Z</t>
+  </si>
+  <si>
+    <t>10 of the most interesting car models headed our way in 2026 | RACQ</t>
+  </si>
+  <si>
+    <t>https://www.racq.com.au/articles/car-updates/10-of-the-most-interesting-car-models-headed-our-way</t>
+  </si>
+  <si>
     <t>articles/road-trip/road-trip-through-central-australia.report.json</t>
   </si>
   <si>
-    <t>["hero-newsletter","cards-article-list","cards-related"]</t>
-  </si>
-  <si>
     <t>articles/road-trip/road-trip-through-central-australia</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>road-trip</t>
   </si>
   <si>
     <t>2026-08-29T10:41:06.737Z</t>
@@ -447,14 +462,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -507,6 +521,32 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
